--- a/docs/Durchlaufzeit_Analyse_2026-08-19.xlsx
+++ b/docs/Durchlaufzeit_Analyse_2026-08-19.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DustinEskofier\Projekt Auftragsbearbeitung\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8E0BDE-E12D-4DB4-BC1C-EEEAAEED8CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8CD04D-770C-4A28-A71F-91B89E694F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übersicht" sheetId="1" r:id="rId1"/>
-    <sheet name="Rohdaten AMM" sheetId="2" r:id="rId2"/>
-    <sheet name="Rohdaten Pipeline" sheetId="3" r:id="rId3"/>
-    <sheet name="Kundenliste" sheetId="4" r:id="rId4"/>
+    <sheet name="Ranking" sheetId="2" r:id="rId2"/>
+    <sheet name="Rohdaten AMM" sheetId="3" r:id="rId3"/>
+    <sheet name="Rohdaten Pipeline" sheetId="4" r:id="rId4"/>
+    <sheet name="Kundenliste" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="427">
   <si>
     <t>Durchlaufzeit-Analyse — Auftrag bis Ware hat Lager verlassen</t>
   </si>
@@ -95,9 +96,180 @@
     <t>• Ab sofort exakt messbar: Auftragstool erfasst startedAt → Lieferstatus 'unterwegs' pro Auftrag (keine Snapshot-Unsicherheit).</t>
   </si>
   <si>
+    <t>Kunden-Ranking — schnellste zuerst</t>
+  </si>
+  <si>
+    <t>AMM-Daten Apr–Aug 2026 · nur Kunden mit ≥ 2 Aufträgen (aussagekräftig) · interner Auftrag Elvinci.de GmbH ausgeschlossen</t>
+  </si>
+  <si>
+    <t>Rang</t>
+  </si>
+  <si>
     <t>Kunde</t>
   </si>
   <si>
+    <t>Aufträge</t>
+  </si>
+  <si>
+    <t>Ø Tage</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Tempo</t>
+  </si>
+  <si>
+    <t>RU Recycling und Umweltdienst GmbH</t>
+  </si>
+  <si>
+    <t>schnell</t>
+  </si>
+  <si>
+    <t>Trade S.R.O. Számlázási</t>
+  </si>
+  <si>
+    <t>Techno Vision Group Ltd</t>
+  </si>
+  <si>
+    <t>Elektro Sinizig</t>
+  </si>
+  <si>
+    <t>Soutis Electrics</t>
+  </si>
+  <si>
+    <t>L&amp;L Electronics Kft</t>
+  </si>
+  <si>
+    <t>Buy4less GmbH</t>
+  </si>
+  <si>
+    <t>Buy24</t>
+  </si>
+  <si>
+    <t>Warriors Cascade Lda</t>
+  </si>
+  <si>
+    <t>Marketvibe Srl</t>
+  </si>
+  <si>
+    <t>Nikokira Outlet</t>
+  </si>
+  <si>
+    <t>P&amp;C Trading B.V.</t>
+  </si>
+  <si>
+    <t>Gujjar Begum</t>
+  </si>
+  <si>
+    <t>Sefik</t>
+  </si>
+  <si>
+    <t>IG international trading GmbH</t>
+  </si>
+  <si>
+    <t>Emporia antalaktikon-Ilektrikon syskeuon</t>
+  </si>
+  <si>
+    <t>mittel</t>
+  </si>
+  <si>
+    <t>UAB Buitikas</t>
+  </si>
+  <si>
+    <t>M&amp;J TRADE D.O.O.</t>
+  </si>
+  <si>
+    <t>Outlet Loket</t>
+  </si>
+  <si>
+    <t>Simex D.O.O</t>
+  </si>
+  <si>
+    <t>(ohne Kundenname)</t>
+  </si>
+  <si>
+    <t>J&amp;B EXPRESS</t>
+  </si>
+  <si>
+    <t>UAB Portana</t>
+  </si>
+  <si>
+    <t>Outlet Simex D.O.O</t>
+  </si>
+  <si>
+    <t>Hanseatic georgia LLC</t>
+  </si>
+  <si>
+    <t>Almost New LTD</t>
+  </si>
+  <si>
+    <t>Kaldi Prime Kft</t>
+  </si>
+  <si>
+    <t>Deland Ltd EOOD</t>
+  </si>
+  <si>
+    <t>Rati Marti</t>
+  </si>
+  <si>
+    <t>SUNELECTRO OÜ</t>
+  </si>
+  <si>
+    <t>KOUTLIANOS NIKOS</t>
+  </si>
+  <si>
+    <t>langsam</t>
+  </si>
+  <si>
+    <t>Egzoni Sh.P.K</t>
+  </si>
+  <si>
+    <t>Alayham Shakantana</t>
+  </si>
+  <si>
+    <t>Todo Cash</t>
+  </si>
+  <si>
+    <t>SADI</t>
+  </si>
+  <si>
+    <t>Banat Electrocasnice S.R.L.</t>
+  </si>
+  <si>
+    <t>TECHNO ELECTRONICS 5 Ltd</t>
+  </si>
+  <si>
+    <t>Ovitshop</t>
+  </si>
+  <si>
+    <t>UAB STEVIJA</t>
+  </si>
+  <si>
+    <t>GGY Trade s.r.o.</t>
+  </si>
+  <si>
+    <t>Hermans Trading BV</t>
+  </si>
+  <si>
+    <t>Outlet Mebeli Ltd</t>
+  </si>
+  <si>
+    <t>AMY Witgoed</t>
+  </si>
+  <si>
+    <t>Euroda Transport &amp;Handel</t>
+  </si>
+  <si>
+    <t>Enterijer D.O.O.</t>
+  </si>
+  <si>
+    <t>Karakitsos Stock House IKE</t>
+  </si>
+  <si>
+    <t>Lesart: Tempo-Terzile über alle gelisteten Kunden. Vorkasse-Kunden erscheinen systembedingt langsamer (warten auf Zahlungseingang) — vor Kundengesprächen Zahlungsart prüfen.</t>
+  </si>
+  <si>
     <t>AU</t>
   </si>
   <si>
@@ -107,21 +279,12 @@
     <t>Unsicherheit (Tage)</t>
   </si>
   <si>
-    <t>Outlet Simex D.O.O</t>
-  </si>
-  <si>
     <t>AU2026021813401</t>
   </si>
   <si>
-    <t>AMY Witgoed</t>
-  </si>
-  <si>
     <t>AU2026022313417</t>
   </si>
   <si>
-    <t>Enterijer D.O.O.</t>
-  </si>
-  <si>
     <t>AU2026022513425</t>
   </si>
   <si>
@@ -137,75 +300,42 @@
     <t>AU2026030614</t>
   </si>
   <si>
-    <t>Karakitsos Stock House IKE</t>
-  </si>
-  <si>
     <t>AU2026030913462</t>
   </si>
   <si>
-    <t>Egzoni Sh.P.K</t>
-  </si>
-  <si>
     <t>AU2026031013467</t>
   </si>
   <si>
-    <t>Euroda Transport &amp;Handel</t>
-  </si>
-  <si>
     <t>AU2026031113475</t>
   </si>
   <si>
-    <t>Hermans Trading BV</t>
-  </si>
-  <si>
     <t>AU2026032013499</t>
   </si>
   <si>
-    <t>Deland Ltd EOOD</t>
-  </si>
-  <si>
     <t>AU2026032013500</t>
   </si>
   <si>
-    <t>Ovitshop</t>
-  </si>
-  <si>
     <t>AU2026032413502</t>
   </si>
   <si>
     <t>AU2026032413506</t>
   </si>
   <si>
-    <t>TECHNO ELECTRONICS 5 Ltd</t>
-  </si>
-  <si>
     <t>AU2026033113525</t>
   </si>
   <si>
-    <t>Hanseatic georgia LLC</t>
-  </si>
-  <si>
     <t>AU2026033113526</t>
   </si>
   <si>
-    <t>Simex D.O.O</t>
-  </si>
-  <si>
     <t>AU2026040113529</t>
   </si>
   <si>
     <t>AU2026040213533</t>
   </si>
   <si>
-    <t>Kaldi Prime Kft</t>
-  </si>
-  <si>
     <t>AU2026032413504</t>
   </si>
   <si>
-    <t>Trade S.R.O. Számlázási</t>
-  </si>
-  <si>
     <t>AU2026040813534</t>
   </si>
   <si>
@@ -215,15 +345,9 @@
     <t>AU2026040813535</t>
   </si>
   <si>
-    <t>Buy4less GmbH</t>
-  </si>
-  <si>
     <t>AU2026040913538</t>
   </si>
   <si>
-    <t>SUNELECTRO OÜ</t>
-  </si>
-  <si>
     <t>AU2026041013539</t>
   </si>
   <si>
@@ -239,21 +363,12 @@
     <t>AU2026041013544</t>
   </si>
   <si>
-    <t>Banat Electrocasnice S.R.L.</t>
-  </si>
-  <si>
     <t>AU2026041013546</t>
   </si>
   <si>
-    <t>M&amp;J TRADE D.O.O.</t>
-  </si>
-  <si>
     <t>AU2026041013547</t>
   </si>
   <si>
-    <t>Almost New LTD</t>
-  </si>
-  <si>
     <t>AU2026041313549</t>
   </si>
   <si>
@@ -275,30 +390,18 @@
     <t>AU2026040113528</t>
   </si>
   <si>
-    <t>IG international trading GmbH</t>
-  </si>
-  <si>
     <t>AU2026041013541</t>
   </si>
   <si>
-    <t>UAB STEVIJA</t>
-  </si>
-  <si>
     <t>AU2026041413554</t>
   </si>
   <si>
-    <t>Marketvibe Srl</t>
-  </si>
-  <si>
     <t>AU2026041413555</t>
   </si>
   <si>
     <t>AU2026041313550</t>
   </si>
   <si>
-    <t>Sefik</t>
-  </si>
-  <si>
     <t>AU2026041413553</t>
   </si>
   <si>
@@ -314,9 +417,6 @@
     <t>AU2026042013574</t>
   </si>
   <si>
-    <t>UAB Portana</t>
-  </si>
-  <si>
     <t>AU2026042113576</t>
   </si>
   <si>
@@ -326,9 +426,6 @@
     <t>AU2026042113577</t>
   </si>
   <si>
-    <t>GGY Trade s.r.o.</t>
-  </si>
-  <si>
     <t>AU2026042113580</t>
   </si>
   <si>
@@ -347,9 +444,6 @@
     <t>AU2026042413593</t>
   </si>
   <si>
-    <t>KOUTLIANOS NIKOS</t>
-  </si>
-  <si>
     <t>AU2026042913603</t>
   </si>
   <si>
@@ -362,9 +456,6 @@
     <t>AU2026050813618</t>
   </si>
   <si>
-    <t>Outlet Mebeli Ltd</t>
-  </si>
-  <si>
     <t>AU2026051113624</t>
   </si>
   <si>
@@ -374,9 +465,6 @@
     <t>AU2026051213627</t>
   </si>
   <si>
-    <t>Todo Cash</t>
-  </si>
-  <si>
     <t>AU2026051313630</t>
   </si>
   <si>
@@ -395,9 +483,6 @@
     <t>AU2026051813642</t>
   </si>
   <si>
-    <t>P&amp;C Trading B.V.</t>
-  </si>
-  <si>
     <t>AU2026051913649</t>
   </si>
   <si>
@@ -410,18 +495,12 @@
     <t>AU2026052113656</t>
   </si>
   <si>
-    <t>Buy24</t>
-  </si>
-  <si>
     <t>AU2026052113657</t>
   </si>
   <si>
     <t>AU2026052113658</t>
   </si>
   <si>
-    <t>Alayham Shakantana</t>
-  </si>
-  <si>
     <t>AU2026052113660</t>
   </si>
   <si>
@@ -464,9 +543,6 @@
     <t>AU2026052713680</t>
   </si>
   <si>
-    <t>Nikokira Outlet</t>
-  </si>
-  <si>
     <t>AU2026052813684</t>
   </si>
   <si>
@@ -488,18 +564,12 @@
     <t>AU2026060113693</t>
   </si>
   <si>
-    <t>Gujjar Begum</t>
-  </si>
-  <si>
     <t>AU2026060213694</t>
   </si>
   <si>
     <t>AU2026060213696</t>
   </si>
   <si>
-    <t>RU Recycling und Umweltdienst GmbH</t>
-  </si>
-  <si>
     <t>AU2026060213697</t>
   </si>
   <si>
@@ -518,9 +588,6 @@
     <t>AU2026060513704</t>
   </si>
   <si>
-    <t>Warriors Cascade Lda</t>
-  </si>
-  <si>
     <t>AU2026060513706</t>
   </si>
   <si>
@@ -548,9 +615,6 @@
     <t>AU2026060913710</t>
   </si>
   <si>
-    <t>(ohne Kundenname)</t>
-  </si>
-  <si>
     <t>AU2026061013715</t>
   </si>
   <si>
@@ -596,15 +660,9 @@
     <t>AU2026061213721</t>
   </si>
   <si>
-    <t>Soutis Electrics</t>
-  </si>
-  <si>
     <t>AU2026061613732</t>
   </si>
   <si>
-    <t>Techno Vision Group Ltd</t>
-  </si>
-  <si>
     <t>AU2026061813746</t>
   </si>
   <si>
@@ -617,9 +675,6 @@
     <t>AU2026061513729</t>
   </si>
   <si>
-    <t>Elektro Sinizig</t>
-  </si>
-  <si>
     <t>AU2026061613733</t>
   </si>
   <si>
@@ -632,18 +687,12 @@
     <t>AU2026062413762</t>
   </si>
   <si>
-    <t>UAB Buitikas</t>
-  </si>
-  <si>
     <t>AU2026062413763</t>
   </si>
   <si>
     <t>AU2026062513764</t>
   </si>
   <si>
-    <t>L&amp;L Electronics Kft</t>
-  </si>
-  <si>
     <t>AU2026062613768</t>
   </si>
   <si>
@@ -773,9 +822,6 @@
     <t>S00312</t>
   </si>
   <si>
-    <t>Emporia antalaktikon-Ilektrikon syskeuon</t>
-  </si>
-  <si>
     <t>S00337</t>
   </si>
   <si>
@@ -785,9 +831,6 @@
     <t>S00340</t>
   </si>
   <si>
-    <t>Rati Marti</t>
-  </si>
-  <si>
     <t>S00354</t>
   </si>
   <si>
@@ -797,9 +840,6 @@
     <t>S00311</t>
   </si>
   <si>
-    <t>SADI</t>
-  </si>
-  <si>
     <t>S00352</t>
   </si>
   <si>
@@ -869,9 +909,6 @@
     <t>S00478</t>
   </si>
   <si>
-    <t>J&amp;B EXPRESS</t>
-  </si>
-  <si>
     <t>S00556</t>
   </si>
   <si>
@@ -900,9 +937,6 @@
   </si>
   <si>
     <t>S00609</t>
-  </si>
-  <si>
-    <t>Outlet Loket</t>
   </si>
   <si>
     <t>S00611</t>
@@ -1294,7 +1328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1337,8 +1371,19 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1350,8 +1395,28 @@
         <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1368,11 +1433,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1393,6 +1467,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1702,7 +1807,7 @@
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1850,6 +1955,1115 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B5)</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B5)</f>
+        <v>2</v>
+      </c>
+      <c r="E5" s="16">
+        <f t="array" ref="E5">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B5,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B6)</f>
+        <v>6</v>
+      </c>
+      <c r="D6" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B6)</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="E6" s="16">
+        <f t="array" ref="E6">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B6,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B7)</f>
+        <v>2</v>
+      </c>
+      <c r="D7" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B7)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="16">
+        <f t="array" ref="E7">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B7,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>3.5</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B8)</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B8)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="16">
+        <f t="array" ref="E8">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B8,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>3.5</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B9)</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B9)</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="16">
+        <f t="array" ref="E9">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B9,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>4</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>6</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B10)</f>
+        <v>2</v>
+      </c>
+      <c r="D10" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B10)</f>
+        <v>5</v>
+      </c>
+      <c r="E10" s="16">
+        <f t="array" ref="E10">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B10,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>5</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>7</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B11)</f>
+        <v>2</v>
+      </c>
+      <c r="D11" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B11)</f>
+        <v>5</v>
+      </c>
+      <c r="E11" s="16">
+        <f t="array" ref="E11">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B11,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>5</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B12)</f>
+        <v>3</v>
+      </c>
+      <c r="D12" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B12)</f>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="E12" s="16">
+        <f t="array" ref="E12">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B12,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>7</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B13)</f>
+        <v>2</v>
+      </c>
+      <c r="D13" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B13)</f>
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="16">
+        <f t="array" ref="E13">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B13,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>5.5</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B14)</f>
+        <v>2</v>
+      </c>
+      <c r="D14" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B14)</f>
+        <v>6</v>
+      </c>
+      <c r="E14" s="16">
+        <f t="array" ref="E14">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B14,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>6</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>11</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B15)</f>
+        <v>3</v>
+      </c>
+      <c r="D15" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B15)</f>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="E15" s="16">
+        <f t="array" ref="E15">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B15,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>8</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B16)</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B16)</f>
+        <v>7</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="array" ref="E16">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B16,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>7.5</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>13</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B17)</f>
+        <v>2</v>
+      </c>
+      <c r="D17" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B17)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E17" s="16">
+        <f t="array" ref="E17">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B17,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>7.5</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>14</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B18)</f>
+        <v>3</v>
+      </c>
+      <c r="D18" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B18)</f>
+        <v>7.666666666666667</v>
+      </c>
+      <c r="E18" s="16">
+        <f t="array" ref="E18">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B18,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>5</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>15</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="16">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B19)</f>
+        <v>9</v>
+      </c>
+      <c r="D19" s="18">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B19)</f>
+        <v>7.7777777777777777</v>
+      </c>
+      <c r="E19" s="16">
+        <f t="array" ref="E19">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B19,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>5</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>16</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B20)</f>
+        <v>2</v>
+      </c>
+      <c r="D20" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B20)</f>
+        <v>8</v>
+      </c>
+      <c r="E20" s="19">
+        <f t="array" ref="E20">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B20,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>8</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>17</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B21)</f>
+        <v>5</v>
+      </c>
+      <c r="D21" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B21)</f>
+        <v>8</v>
+      </c>
+      <c r="E21" s="19">
+        <f t="array" ref="E21">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B21,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>9</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>18</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B22)</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B22)</f>
+        <v>8</v>
+      </c>
+      <c r="E22" s="19">
+        <f t="array" ref="E22">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B22,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>8</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>19</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B23)</f>
+        <v>2</v>
+      </c>
+      <c r="D23" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B23)</f>
+        <v>9</v>
+      </c>
+      <c r="E23" s="19">
+        <f t="array" ref="E23">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B23,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>9</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>20</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B24)</f>
+        <v>3</v>
+      </c>
+      <c r="D24" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B24)</f>
+        <v>9</v>
+      </c>
+      <c r="E24" s="19">
+        <f t="array" ref="E24">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B24,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>7</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>21</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B25)</f>
+        <v>3</v>
+      </c>
+      <c r="D25" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B25)</f>
+        <v>9</v>
+      </c>
+      <c r="E25" s="19">
+        <f t="array" ref="E25">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B25,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>9</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>22</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B26)</f>
+        <v>3</v>
+      </c>
+      <c r="D26" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B26)</f>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="E26" s="19">
+        <f t="array" ref="E26">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B26,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>11</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>23</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B27)</f>
+        <v>4</v>
+      </c>
+      <c r="D27" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B27)</f>
+        <v>11.75</v>
+      </c>
+      <c r="E27" s="19">
+        <f t="array" ref="E27">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B27,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>12.5</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>24</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B28)</f>
+        <v>5</v>
+      </c>
+      <c r="D28" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B28)</f>
+        <v>11.8</v>
+      </c>
+      <c r="E28" s="19">
+        <f t="array" ref="E28">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B28,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>4</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>25</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B29)</f>
+        <v>11</v>
+      </c>
+      <c r="D29" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B29)</f>
+        <v>12.272727272727273</v>
+      </c>
+      <c r="E29" s="19">
+        <f t="array" ref="E29">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B29,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>12</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>26</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B30)</f>
+        <v>2</v>
+      </c>
+      <c r="D30" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B30)</f>
+        <v>13</v>
+      </c>
+      <c r="E30" s="19">
+        <f t="array" ref="E30">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B30,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>13</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>27</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B31)</f>
+        <v>3</v>
+      </c>
+      <c r="D31" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B31)</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="E31" s="19">
+        <f t="array" ref="E31">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B31,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>12</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>28</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B32)</f>
+        <v>3</v>
+      </c>
+      <c r="D32" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B32)</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="E32" s="19">
+        <f t="array" ref="E32">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B32,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>15</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>29</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B33)</f>
+        <v>2</v>
+      </c>
+      <c r="D33" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B33)</f>
+        <v>14.5</v>
+      </c>
+      <c r="E33" s="19">
+        <f t="array" ref="E33">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B33,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>30</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="19">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B34)</f>
+        <v>2</v>
+      </c>
+      <c r="D34" s="21">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B34)</f>
+        <v>14.5</v>
+      </c>
+      <c r="E34" s="19">
+        <f t="array" ref="E34">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B34,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>14.5</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="22">
+        <v>31</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B35)</f>
+        <v>5</v>
+      </c>
+      <c r="D35" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B35)</f>
+        <v>14.8</v>
+      </c>
+      <c r="E35" s="22">
+        <f t="array" ref="E35">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B35,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>11</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="22">
+        <v>32</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B36)</f>
+        <v>4</v>
+      </c>
+      <c r="D36" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B36)</f>
+        <v>15</v>
+      </c>
+      <c r="E36" s="22">
+        <f t="array" ref="E36">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B36,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>15</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="22">
+        <v>33</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B37)</f>
+        <v>2</v>
+      </c>
+      <c r="D37" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B37)</f>
+        <v>15.5</v>
+      </c>
+      <c r="E37" s="22">
+        <f t="array" ref="E37">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B37,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>15.5</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="22">
+        <v>34</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B38)</f>
+        <v>2</v>
+      </c>
+      <c r="D38" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B38)</f>
+        <v>16</v>
+      </c>
+      <c r="E38" s="22">
+        <f t="array" ref="E38">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B38,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>16</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="22">
+        <v>35</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B39)</f>
+        <v>2</v>
+      </c>
+      <c r="D39" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B39)</f>
+        <v>16</v>
+      </c>
+      <c r="E39" s="22">
+        <f t="array" ref="E39">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B39,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>16</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="22">
+        <v>36</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B40)</f>
+        <v>4</v>
+      </c>
+      <c r="D40" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B40)</f>
+        <v>16.5</v>
+      </c>
+      <c r="E40" s="22">
+        <f t="array" ref="E40">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B40,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>15</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="22">
+        <v>37</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B41)</f>
+        <v>4</v>
+      </c>
+      <c r="D41" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B41)</f>
+        <v>18</v>
+      </c>
+      <c r="E41" s="22">
+        <f t="array" ref="E41">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B41,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>12</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="22">
+        <v>38</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B42)</f>
+        <v>7</v>
+      </c>
+      <c r="D42" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B42)</f>
+        <v>20</v>
+      </c>
+      <c r="E42" s="22">
+        <f t="array" ref="E42">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B42,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>7</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="22">
+        <v>39</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B43)</f>
+        <v>6</v>
+      </c>
+      <c r="D43" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B43)</f>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="E43" s="22">
+        <f t="array" ref="E43">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B43,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>20.5</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="22">
+        <v>40</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B44)</f>
+        <v>2</v>
+      </c>
+      <c r="D44" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B44)</f>
+        <v>22</v>
+      </c>
+      <c r="E44" s="22">
+        <f t="array" ref="E44">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B44,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>22</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="22">
+        <v>41</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B45)</f>
+        <v>7</v>
+      </c>
+      <c r="D45" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B45)</f>
+        <v>23.571428571428573</v>
+      </c>
+      <c r="E45" s="22">
+        <f t="array" ref="E45">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B45,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>12</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="22">
+        <v>42</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B46)</f>
+        <v>2</v>
+      </c>
+      <c r="D46" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B46)</f>
+        <v>25</v>
+      </c>
+      <c r="E46" s="22">
+        <f t="array" ref="E46">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B46,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>25</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="22">
+        <v>43</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B47)</f>
+        <v>4</v>
+      </c>
+      <c r="D47" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B47)</f>
+        <v>26</v>
+      </c>
+      <c r="E47" s="22">
+        <f t="array" ref="E47">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B47,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>26</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="22">
+        <v>44</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B48)</f>
+        <v>2</v>
+      </c>
+      <c r="D48" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B48)</f>
+        <v>29.5</v>
+      </c>
+      <c r="E48" s="22">
+        <f t="array" ref="E48">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B48,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>29.5</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="22">
+        <v>45</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B49)</f>
+        <v>2</v>
+      </c>
+      <c r="D49" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B49)</f>
+        <v>34</v>
+      </c>
+      <c r="E49" s="22">
+        <f t="array" ref="E49">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B49,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>34</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="22">
+        <v>46</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="22">
+        <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$B50)</f>
+        <v>3</v>
+      </c>
+      <c r="D50" s="24">
+        <f>AVERAGEIFS('Rohdaten AMM'!$C$2:$C$194,'Rohdaten AMM'!$A$2:$A$194,$B50)</f>
+        <v>34.666666666666664</v>
+      </c>
+      <c r="E50" s="22">
+        <f t="array" ref="E50">MEDIAN(IF('Rohdaten AMM'!$A$2:$A$194=$B50,'Rohdaten AMM'!$C$2:$C$194))</f>
+        <v>8</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1861,24 +3075,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3">
         <v>39</v>
@@ -1889,10 +3103,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
         <v>48</v>
@@ -1903,10 +3117,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C4" s="3">
         <v>66</v>
@@ -1917,10 +3131,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C5" s="3">
         <v>37</v>
@@ -1931,10 +3145,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3">
         <v>85</v>
@@ -1945,10 +3159,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3">
         <v>88</v>
@@ -1959,10 +3173,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="C8" s="3">
         <v>21</v>
@@ -1973,10 +3187,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C9" s="3">
         <v>14</v>
@@ -1987,10 +3201,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3">
         <v>12</v>
@@ -2001,10 +3215,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3">
         <v>17</v>
@@ -2015,10 +3229,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3">
         <v>81</v>
@@ -2029,10 +3243,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="C13" s="3">
         <v>101</v>
@@ -2043,10 +3257,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
@@ -2057,10 +3271,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3">
         <v>14</v>
@@ -2071,10 +3285,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3">
         <v>7</v>
@@ -2085,10 +3299,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
@@ -2099,10 +3313,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="C18" s="3">
         <v>6</v>
@@ -2113,10 +3327,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
@@ -2127,10 +3341,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C20" s="3">
         <v>7</v>
@@ -2141,10 +3355,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C21" s="3">
         <v>3</v>
@@ -2155,10 +3369,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="C22" s="3">
         <v>4</v>
@@ -2169,10 +3383,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="C23" s="3">
         <v>29</v>
@@ -2183,10 +3397,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3">
         <v>2</v>
@@ -2197,10 +3411,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C25" s="3">
         <v>7</v>
@@ -2211,10 +3425,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C26" s="3">
         <v>10</v>
@@ -2225,10 +3439,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -2239,10 +3453,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C28" s="3">
         <v>25</v>
@@ -2253,10 +3467,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C29" s="3">
         <v>6</v>
@@ -2267,10 +3481,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C30" s="3">
         <v>25</v>
@@ -2281,10 +3495,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
@@ -2295,10 +3509,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C32" s="3">
         <v>4</v>
@@ -2309,10 +3523,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C33" s="3">
         <v>5</v>
@@ -2323,10 +3537,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3">
         <v>23</v>
@@ -2337,10 +3551,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="C35" s="3">
         <v>4</v>
@@ -2351,10 +3565,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C36" s="3">
         <v>18</v>
@@ -2365,10 +3579,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="C37" s="3">
         <v>16</v>
@@ -2379,10 +3593,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C38" s="3">
         <v>18</v>
@@ -2393,10 +3607,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C39" s="3">
         <v>16</v>
@@ -2407,10 +3621,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="C40" s="3">
         <v>18</v>
@@ -2421,10 +3635,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C41" s="3">
         <v>16</v>
@@ -2435,10 +3649,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -2449,10 +3663,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="C43" s="3">
         <v>17</v>
@@ -2463,10 +3677,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="C44" s="3">
         <v>17</v>
@@ -2477,10 +3691,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="C45" s="3">
         <v>0</v>
@@ -2491,10 +3705,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="C46" s="3">
         <v>16</v>
@@ -2505,10 +3719,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="C47" s="3">
         <v>16</v>
@@ -2519,10 +3733,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="C48" s="3">
         <v>45</v>
@@ -2533,10 +3747,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C49" s="3">
         <v>30</v>
@@ -2547,10 +3761,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="C50" s="3">
         <v>39</v>
@@ -2561,10 +3775,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C51" s="3">
         <v>11</v>
@@ -2575,10 +3789,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C52" s="3">
         <v>14</v>
@@ -2589,10 +3803,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C53" s="3">
         <v>12</v>
@@ -2603,10 +3817,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C54" s="3">
         <v>26</v>
@@ -2617,10 +3831,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C55" s="3">
         <v>19</v>
@@ -2631,10 +3845,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C56" s="3">
         <v>14</v>
@@ -2645,10 +3859,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C57" s="3">
         <v>8</v>
@@ -2659,10 +3873,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="C58" s="3">
         <v>8</v>
@@ -2673,10 +3887,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C59" s="3">
         <v>18</v>
@@ -2687,10 +3901,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C60" s="3">
         <v>10</v>
@@ -2701,10 +3915,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C61" s="3">
         <v>8</v>
@@ -2715,10 +3929,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C62" s="3">
         <v>36</v>
@@ -2729,10 +3943,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C63" s="3">
         <v>13</v>
@@ -2743,10 +3957,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C64" s="3">
         <v>7</v>
@@ -2757,10 +3971,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C65" s="3">
         <v>7</v>
@@ -2771,10 +3985,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C66" s="3">
         <v>18</v>
@@ -2785,10 +3999,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C67" s="3">
         <v>7</v>
@@ -2799,10 +4013,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
@@ -2813,10 +4027,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C69" s="3">
         <v>3</v>
@@ -2827,10 +4041,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C70" s="3">
         <v>45</v>
@@ -2841,10 +4055,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C71" s="3">
         <v>8</v>
@@ -2855,10 +4069,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C72" s="3">
         <v>5</v>
@@ -2869,10 +4083,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C73" s="3">
         <v>8</v>
@@ -2883,10 +4097,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C74" s="3">
         <v>27</v>
@@ -2897,10 +4111,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C75" s="3">
         <v>2</v>
@@ -2911,10 +4125,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C76" s="3">
         <v>13</v>
@@ -2925,10 +4139,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C77" s="3">
         <v>11</v>
@@ -2939,10 +4153,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C78" s="3">
         <v>8</v>
@@ -2953,10 +4167,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C79" s="3">
         <v>11</v>
@@ -2967,10 +4181,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C80" s="3">
         <v>8</v>
@@ -2981,10 +4195,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C81" s="3">
         <v>8</v>
@@ -2995,10 +4209,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C82" s="3">
         <v>11</v>
@@ -3009,10 +4223,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C83" s="3">
         <v>5</v>
@@ -3023,10 +4237,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="C84" s="3">
         <v>14</v>
@@ -3037,10 +4251,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C85" s="3">
         <v>7</v>
@@ -3051,10 +4265,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C86" s="3">
         <v>3</v>
@@ -3065,10 +4279,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C87" s="3">
         <v>6</v>
@@ -3079,10 +4293,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C88" s="3">
         <v>15</v>
@@ -3093,10 +4307,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C89" s="3">
         <v>5</v>
@@ -3107,10 +4321,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C90" s="3">
         <v>10</v>
@@ -3121,10 +4335,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C91" s="3">
         <v>3</v>
@@ -3135,10 +4349,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C92" s="3">
         <v>4</v>
@@ -3149,10 +4363,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C93" s="3">
         <v>12</v>
@@ -3163,10 +4377,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C94" s="3">
         <v>8</v>
@@ -3177,10 +4391,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C95" s="3">
         <v>23</v>
@@ -3191,10 +4405,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C96" s="3">
         <v>6</v>
@@ -3205,10 +4419,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C97" s="3">
         <v>2</v>
@@ -3219,10 +4433,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C98" s="3">
         <v>28</v>
@@ -3233,10 +4447,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C99" s="3">
         <v>5</v>
@@ -3247,10 +4461,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C100" s="3">
         <v>5</v>
@@ -3261,10 +4475,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C101" s="3">
         <v>9</v>
@@ -3275,10 +4489,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C102" s="3">
         <v>17</v>
@@ -3289,10 +4503,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C103" s="3">
         <v>5</v>
@@ -3303,10 +4517,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C104" s="3">
         <v>0</v>
@@ -3317,10 +4531,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C105" s="3">
         <v>1</v>
@@ -3331,10 +4545,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C106" s="3">
         <v>3</v>
@@ -3345,10 +4559,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C107" s="3">
         <v>9</v>
@@ -3359,10 +4573,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C108" s="3">
         <v>2</v>
@@ -3373,10 +4587,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C109" s="3">
         <v>22</v>
@@ -3387,10 +4601,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C110" s="3">
         <v>26</v>
@@ -3401,10 +4615,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C111" s="3">
         <v>2</v>
@@ -3415,10 +4629,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C112" s="3">
         <v>14</v>
@@ -3429,10 +4643,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>186</v>
+        <v>32</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C113" s="3">
         <v>6</v>
@@ -3443,10 +4657,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C114" s="3">
         <v>6</v>
@@ -3457,10 +4671,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>186</v>
+        <v>32</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C115" s="3">
         <v>2</v>
@@ -3471,10 +4685,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C116" s="3">
         <v>15</v>
@@ -3485,10 +4699,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C117" s="3">
         <v>18</v>
@@ -3499,10 +4713,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C118" s="3">
         <v>5</v>
@@ -3513,10 +4727,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C119" s="3">
         <v>3</v>
@@ -3527,10 +4741,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C120" s="3">
         <v>14</v>
@@ -3541,10 +4755,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C121" s="3">
         <v>8</v>
@@ -3555,10 +4769,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C122" s="3">
         <v>14</v>
@@ -3569,10 +4783,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C123" s="3">
         <v>13</v>
@@ -3583,10 +4797,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C124" s="3">
         <v>5</v>
@@ -3597,10 +4811,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C125" s="3">
         <v>3</v>
@@ -3611,10 +4825,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C126" s="3">
         <v>7</v>
@@ -3625,10 +4839,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C127" s="3">
         <v>0</v>
@@ -3639,10 +4853,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C128" s="3">
         <v>5</v>
@@ -3653,10 +4867,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C129" s="3">
         <v>13</v>
@@ -3667,10 +4881,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C130" s="3">
         <v>9</v>
@@ -3681,10 +4895,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="C131" s="3">
         <v>13</v>
@@ -3695,10 +4909,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C132" s="3">
         <v>9</v>
@@ -3709,10 +4923,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="C133" s="3">
         <v>2</v>
@@ -3723,10 +4937,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C134" s="3">
         <v>37</v>
@@ -3737,10 +4951,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="C135" s="3">
         <v>2</v>
@@ -3751,10 +4965,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C136" s="3">
         <v>2</v>
@@ -3765,10 +4979,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C137" s="3">
         <v>13</v>
@@ -3779,10 +4993,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C138" s="3">
         <v>15</v>
@@ -3793,10 +5007,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C139" s="3">
         <v>11</v>
@@ -3807,10 +5021,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C140" s="3">
         <v>31</v>
@@ -3821,10 +5035,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="C141" s="3">
         <v>7</v>
@@ -3835,10 +5049,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C142" s="3">
         <v>2</v>
@@ -3849,10 +5063,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="C143" s="3">
         <v>3</v>
@@ -3863,10 +5077,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C144" s="3">
         <v>2</v>
@@ -3877,10 +5091,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="C145" s="3">
         <v>2</v>
@@ -3891,10 +5105,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C146" s="3">
         <v>30</v>
@@ -3905,10 +5119,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C147" s="3">
         <v>2</v>
@@ -3919,10 +5133,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="C148" s="3">
         <v>6</v>
@@ -3933,10 +5147,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="C149" s="3">
         <v>6</v>
@@ -3947,10 +5161,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C150" s="3">
         <v>4</v>
@@ -3961,10 +5175,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C151" s="3">
         <v>5</v>
@@ -3975,10 +5189,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C152" s="3">
         <v>1</v>
@@ -3989,10 +5203,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C153" s="3">
         <v>1</v>
@@ -4003,10 +5217,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C154" s="3">
         <v>1</v>
@@ -4017,10 +5231,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
@@ -4031,10 +5245,10 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
@@ -4045,10 +5259,10 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="C157" s="3">
         <v>3</v>
@@ -4059,10 +5273,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C158" s="3">
         <v>6</v>
@@ -4073,10 +5287,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="C159" s="3">
         <v>1</v>
@@ -4087,10 +5301,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
@@ -4101,10 +5315,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C161" s="3">
         <v>4</v>
@@ -4115,10 +5329,10 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>249</v>
+        <v>57</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C162" s="3">
         <v>20</v>
@@ -4129,10 +5343,10 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C163" s="3">
         <v>5</v>
@@ -4143,10 +5357,10 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C164" s="3">
         <v>18</v>
@@ -4157,10 +5371,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -4171,10 +5385,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C166" s="3">
         <v>4</v>
@@ -4185,10 +5399,10 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C167" s="3">
         <v>15</v>
@@ -4199,10 +5413,10 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C168" s="3">
         <v>16</v>
@@ -4213,10 +5427,10 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C169" s="3">
         <v>16</v>
@@ -4227,10 +5441,10 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C170" s="3">
         <v>15</v>
@@ -4241,10 +5455,10 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C171" s="3">
         <v>3</v>
@@ -4255,10 +5469,10 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C172" s="3">
         <v>15</v>
@@ -4269,10 +5483,10 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C173" s="3">
         <v>15</v>
@@ -4283,10 +5497,10 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C174" s="3">
         <v>15</v>
@@ -4297,10 +5511,10 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C175" s="3">
         <v>2</v>
@@ -4311,10 +5525,10 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C176" s="3">
         <v>2</v>
@@ -4325,10 +5539,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C177" s="3">
         <v>14</v>
@@ -4339,10 +5553,10 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C178" s="3">
         <v>14</v>
@@ -4353,10 +5567,10 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C179" s="3">
         <v>14</v>
@@ -4367,10 +5581,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C180" s="3">
         <v>10</v>
@@ -4381,10 +5595,10 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>277</v>
+        <v>50</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C181" s="3">
         <v>11</v>
@@ -4395,10 +5609,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C182" s="3">
         <v>13</v>
@@ -4409,10 +5623,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>277</v>
+        <v>50</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C183" s="3">
         <v>11</v>
@@ -4423,10 +5637,10 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>277</v>
+        <v>50</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C184" s="3">
         <v>10</v>
@@ -4437,10 +5651,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C185" s="3">
         <v>10</v>
@@ -4451,10 +5665,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>249</v>
+        <v>57</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C186" s="3">
         <v>9</v>
@@ -4465,10 +5679,10 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C187" s="3">
         <v>10</v>
@@ -4479,10 +5693,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C188" s="3">
         <v>10</v>
@@ -4493,10 +5707,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C189" s="3">
         <v>9</v>
@@ -4507,10 +5721,10 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C190" s="3">
         <v>9</v>
@@ -4521,10 +5735,10 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C191" s="3">
         <v>9</v>
@@ -4535,10 +5749,10 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C192" s="3">
         <v>9</v>
@@ -4549,10 +5763,10 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C193" s="3">
         <v>9</v>
@@ -4563,10 +5777,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C194" s="3">
         <v>9</v>
@@ -4580,8 +5794,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4593,21 +5807,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C2" s="3">
         <v>4</v>
@@ -4615,10 +5829,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="C3" s="3">
         <v>4</v>
@@ -4626,10 +5840,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C4" s="3">
         <v>8</v>
@@ -4637,10 +5851,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C5" s="3">
         <v>8</v>
@@ -4648,10 +5862,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="C6" s="3">
         <v>6</v>
@@ -4659,10 +5873,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C7" s="3">
         <v>15</v>
@@ -4670,10 +5884,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C8" s="3">
         <v>11</v>
@@ -4681,10 +5895,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C9" s="3">
         <v>7</v>
@@ -4692,10 +5906,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C10" s="3">
         <v>8</v>
@@ -4703,10 +5917,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C11" s="3">
         <v>7</v>
@@ -4714,10 +5928,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C12" s="3">
         <v>5</v>
@@ -4725,10 +5939,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C13" s="3">
         <v>5</v>
@@ -4736,10 +5950,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C14" s="3">
         <v>6</v>
@@ -4747,10 +5961,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C15" s="3">
         <v>6</v>
@@ -4758,10 +5972,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C16" s="3">
         <v>6</v>
@@ -4769,10 +5983,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C17" s="3">
         <v>4</v>
@@ -4780,10 +5994,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C18" s="3">
         <v>6</v>
@@ -4791,10 +6005,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="C19" s="3">
         <v>5</v>
@@ -4802,10 +6016,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C20" s="3">
         <v>7</v>
@@ -4813,10 +6027,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C21" s="3">
         <v>4</v>
@@ -4824,10 +6038,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C22" s="3">
         <v>6</v>
@@ -4835,10 +6049,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C23" s="3">
         <v>5</v>
@@ -4846,10 +6060,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C24" s="3">
         <v>11</v>
@@ -4857,10 +6071,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C25" s="3">
         <v>6</v>
@@ -4868,10 +6082,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="C26" s="3">
         <v>21</v>
@@ -4879,10 +6093,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C27" s="3">
         <v>18</v>
@@ -4890,10 +6104,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C28" s="3">
         <v>15</v>
@@ -4901,10 +6115,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="C29" s="3">
         <v>14</v>
@@ -4912,10 +6126,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C30" s="3">
         <v>10</v>
@@ -4923,10 +6137,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C31" s="3">
         <v>16</v>
@@ -4934,10 +6148,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C32" s="3">
         <v>13</v>
@@ -4945,10 +6159,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C33" s="3">
         <v>7</v>
@@ -4956,10 +6170,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C34" s="3">
         <v>7</v>
@@ -4967,10 +6181,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C35" s="3">
         <v>6</v>
@@ -4978,10 +6192,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C36" s="3">
         <v>8</v>
@@ -4989,10 +6203,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C37" s="3">
         <v>18</v>
@@ -5000,10 +6214,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C38" s="3">
         <v>7</v>
@@ -5011,10 +6225,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C39" s="3">
         <v>10</v>
@@ -5022,10 +6236,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="C40" s="3">
         <v>14</v>
@@ -5033,10 +6247,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C41" s="3">
         <v>9</v>
@@ -5044,10 +6258,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C42" s="3">
         <v>9</v>
@@ -5055,10 +6269,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="C43" s="3">
         <v>12</v>
@@ -5066,10 +6280,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C44" s="3">
         <v>7</v>
@@ -5077,10 +6291,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C45" s="3">
         <v>11</v>
@@ -5088,10 +6302,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="C46" s="3">
         <v>7</v>
@@ -5099,10 +6313,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C47" s="3">
         <v>6</v>
@@ -5110,10 +6324,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="C48" s="3">
         <v>5</v>
@@ -5121,10 +6335,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="C49" s="3">
         <v>4</v>
@@ -5132,10 +6346,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C50" s="3">
         <v>6</v>
@@ -5143,10 +6357,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C51" s="3">
         <v>3</v>
@@ -5154,10 +6368,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C52" s="3">
         <v>9</v>
@@ -5165,10 +6379,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C53" s="3">
         <v>2</v>
@@ -5176,10 +6390,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C54" s="3">
         <v>2</v>
@@ -5187,10 +6401,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C55" s="3">
         <v>5</v>
@@ -5198,10 +6412,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C56" s="3">
         <v>11</v>
@@ -5209,10 +6423,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C57" s="3">
         <v>7</v>
@@ -5220,10 +6434,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C58" s="3">
         <v>13</v>
@@ -5231,10 +6445,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="C59" s="3">
         <v>7</v>
@@ -5242,10 +6456,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C60" s="3">
         <v>9</v>
@@ -5253,10 +6467,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C61" s="3">
         <v>3</v>
@@ -5264,10 +6478,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C62" s="3">
         <v>11</v>
@@ -5275,10 +6489,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C63" s="3">
         <v>8</v>
@@ -5286,10 +6500,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C64" s="3">
         <v>5</v>
@@ -5297,10 +6511,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C65" s="3">
         <v>5</v>
@@ -5308,10 +6522,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C66" s="3">
         <v>21</v>
@@ -5319,10 +6533,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C67" s="3">
         <v>6</v>
@@ -5330,10 +6544,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C68" s="3">
         <v>2</v>
@@ -5341,10 +6555,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C69" s="3">
         <v>28</v>
@@ -5352,10 +6566,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C70" s="3">
         <v>8</v>
@@ -5363,10 +6577,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C71" s="3">
         <v>14</v>
@@ -5374,10 +6588,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C72" s="3">
         <v>9</v>
@@ -5385,10 +6599,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C73" s="3">
         <v>14</v>
@@ -5396,10 +6610,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="C74" s="3">
         <v>6</v>
@@ -5407,10 +6621,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C75" s="3">
         <v>11</v>
@@ -5418,10 +6632,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C76" s="3">
         <v>6</v>
@@ -5429,10 +6643,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C77" s="3">
         <v>7</v>
@@ -5440,10 +6654,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C78" s="3">
         <v>6</v>
@@ -5451,10 +6665,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C79" s="3">
         <v>7</v>
@@ -5462,10 +6676,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C80" s="3">
         <v>6</v>
@@ -5473,10 +6687,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C81" s="3">
         <v>3</v>
@@ -5484,10 +6698,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C82" s="3">
         <v>6</v>
@@ -5495,10 +6709,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C83" s="3">
         <v>2</v>
@@ -5506,10 +6720,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C84" s="3">
         <v>4</v>
@@ -5517,10 +6731,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C85" s="3">
         <v>8</v>
@@ -5528,10 +6742,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C86" s="3">
         <v>9</v>
@@ -5539,10 +6753,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C87" s="3">
         <v>4</v>
@@ -5550,10 +6764,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -5561,10 +6775,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="C89" s="3">
         <v>4</v>
@@ -5575,8 +6789,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5589,45 +6803,45 @@
     <col min="8" max="8" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="B5" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A5)</f>
@@ -5660,7 +6874,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="B6" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A6)</f>
@@ -5693,7 +6907,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A7)</f>
@@ -5726,7 +6940,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A8)</f>
@@ -5759,7 +6973,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="B9" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A9)</f>
@@ -5792,7 +7006,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B10" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A10)</f>
@@ -5825,7 +7039,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B11" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A11)</f>
@@ -5858,7 +7072,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B12" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A12)</f>
@@ -5891,7 +7105,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="B13" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A13)</f>
@@ -5924,7 +7138,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B14" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A14)</f>
@@ -5957,7 +7171,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B15" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A15)</f>
@@ -5990,7 +7204,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B16" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A16)</f>
@@ -6023,7 +7237,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A17)</f>
@@ -6056,7 +7270,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B18" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A18)</f>
@@ -6089,7 +7303,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="B19" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A19)</f>
@@ -6122,7 +7336,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A20)</f>
@@ -6155,7 +7369,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="B21" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A21)</f>
@@ -6188,7 +7402,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="B22" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A22)</f>
@@ -6221,7 +7435,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B23" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A23)</f>
@@ -6254,7 +7468,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A24)</f>
@@ -6287,7 +7501,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B25" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A25)</f>
@@ -6320,7 +7534,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B26" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A26)</f>
@@ -6353,7 +7567,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B27" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A27)</f>
@@ -6386,7 +7600,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B28" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A28)</f>
@@ -6419,7 +7633,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B29" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A29)</f>
@@ -6452,7 +7666,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>249</v>
+        <v>57</v>
       </c>
       <c r="B30" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A30)</f>
@@ -6485,7 +7699,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="B31" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A31)</f>
@@ -6518,7 +7732,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B32" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A32)</f>
@@ -6551,7 +7765,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B33" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A33)</f>
@@ -6584,7 +7798,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B34" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A34)</f>
@@ -6617,7 +7831,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B35" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A35)</f>
@@ -6650,7 +7864,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B36" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A36)</f>
@@ -6683,7 +7897,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B37" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A37)</f>
@@ -6716,7 +7930,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B38" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A38)</f>
@@ -6749,7 +7963,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B39" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A39)</f>
@@ -6782,7 +7996,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="B40" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A40)</f>
@@ -6815,7 +8029,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>277</v>
+        <v>50</v>
       </c>
       <c r="B41" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A41)</f>
@@ -6848,7 +8062,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B42" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A42)</f>
@@ -6881,7 +8095,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B43" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A43)</f>
@@ -6914,7 +8128,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B44" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A44)</f>
@@ -6947,7 +8161,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="B45" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A45)</f>
@@ -6980,7 +8194,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
       <c r="B46" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A46)</f>
@@ -7013,7 +8227,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B47" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A47)</f>
@@ -7046,7 +8260,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B48" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A48)</f>
@@ -7079,7 +8293,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="B49" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A49)</f>
@@ -7112,7 +8326,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="B50" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A50)</f>
@@ -7145,7 +8359,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B51" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A51)</f>
@@ -7178,7 +8392,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B52" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A52)</f>
@@ -7211,7 +8425,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="B53" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A53)</f>
@@ -7244,7 +8458,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B54" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A54)</f>
@@ -7277,7 +8491,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="B55" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A55)</f>
@@ -7310,7 +8524,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="B56" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A56)</f>
@@ -7343,7 +8557,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B57" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A57)</f>
@@ -7376,7 +8590,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B58" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A58)</f>
@@ -7409,7 +8623,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B59" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A59)</f>
@@ -7442,7 +8656,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B60" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A60)</f>
@@ -7475,7 +8689,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="B61" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A61)</f>
@@ -7508,7 +8722,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="B62" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A62)</f>
@@ -7541,7 +8755,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B63" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A63)</f>
@@ -7574,7 +8788,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="B64" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A64)</f>
@@ -7607,7 +8821,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B65" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A65)</f>
@@ -7640,7 +8854,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>201</v>
+        <v>33</v>
       </c>
       <c r="B66" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A66)</f>
@@ -7673,7 +8887,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B67" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A67)</f>
@@ -7706,7 +8920,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>186</v>
+        <v>32</v>
       </c>
       <c r="B68" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A68)</f>
@@ -7739,7 +8953,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B69" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A69)</f>
@@ -7772,7 +8986,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="B70" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A70)</f>
@@ -7805,7 +9019,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
       <c r="B71" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A71)</f>
@@ -7838,7 +9052,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B72" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A72)</f>
@@ -7871,7 +9085,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B73" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A73)</f>
@@ -7904,7 +9118,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="B74" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A74)</f>
@@ -7937,7 +9151,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B75" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A75)</f>
@@ -7970,7 +9184,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="B76" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A76)</f>
@@ -8003,7 +9217,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B77" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A77)</f>
@@ -8036,7 +9250,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B78" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A78)</f>
@@ -8069,7 +9283,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="B79" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A79)</f>
@@ -8102,7 +9316,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B80" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A80)</f>
@@ -8135,7 +9349,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B81" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A81)</f>
@@ -8168,7 +9382,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B82" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A82)</f>
@@ -8201,7 +9415,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B83" s="11">
         <f>COUNTIFS('Rohdaten AMM'!$A$2:$A$194,$A83)</f>
